--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/PENNSYLVANIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/PENNSYLVANIA_2013.xlsx
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C185">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C513">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C531">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C887">
